--- a/characters.xlsx
+++ b/characters.xlsx
@@ -1,5720 +1,6216 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Inquisitorial Agent" sheetId="1" r:id="rId1"/>
-    <sheet name="Sanctioned Psyker" sheetId="2" r:id="rId2"/>
-    <sheet name="Aeldari Corsair" sheetId="3" r:id="rId3"/>
-    <sheet name="The Swashbuckling Dynasty Heir" sheetId="4" r:id="rId4"/>
-    <sheet name="The Archeotech Sanctifier" sheetId="5" r:id="rId5"/>
-    <sheet name="The Void-Breacher Veteran" sheetId="6" r:id="rId6"/>
-    <sheet name="The Void-Eye Scion" sheetId="7" r:id="rId7"/>
-    <sheet name="The Ork Waaagh!-Shaman" sheetId="8" r:id="rId8"/>
-    <sheet name="The Red Consecrator" sheetId="9" r:id="rId9"/>
-    <sheet name="The Untouchable Witch Finder" sheetId="10" r:id="rId10"/>
-    <sheet name="The Heretek Tech-Acolyte" sheetId="11" r:id="rId11"/>
-    <sheet name="The Exiled House Visscher Navig" sheetId="12" r:id="rId12"/>
-    <sheet name="The Beast-Master Privateer" sheetId="13" r:id="rId13"/>
+    <sheet name="Inquisitorial Agent" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sanctioned Psyker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aeldari Corsair" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="The Swashbuckling Dynasty Heir" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="The Archeotech Sanctifier" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="The Void-Breacher Veteran" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="The Void-Eye Scion" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="The Ork Waaagh!-Shaman" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="The Red Consecrator" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="The Untouchable Witch Finder" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="The Heretek Tech-Acolyte" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="The Exiled House Visscher Navig" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="The Beast-Master Privateer" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inquisitorial Agent</t>
+          <t>Inquisitorial Agent</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneschal (Inquisitorial Representative)</t>
+          <t>Seneschal (Inquisitorial Representative)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spymaster, political liaison, and covert handler ensuring the Rogue Trader's dynasty remains compliant with Imperial law.</t>
+          <t>Spymaster, political liaison, and covert handler ensuring the Rogue Trader's dynasty remains compliant with Imperial law.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imperial World</t>
+          <t>Imperial World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savant</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">High Vendetta</t>
+          <t>High Vendetta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestige</t>
+          <t>Prestige</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneschal</t>
+          <t>Seneschal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound: Duty to the Throne</t>
+          <t>Duty Bound: Duty to the Throne</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeker of Lore (Spend a Fate Point to automatically succeed at any Ciphers, Lore, or Logic test in minimum time; +1 bonus Degree of Success on Commerce, Inquiry, or Evaluate tests).</t>
+          <t>Seeker of Lore (Spend a Fate Point to automatically succeed at any Ciphers, Lore, or Logic test in minimum time; +1 bonus Degree of Success on Commerce, Inquiry, or Evaluate tests).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, The Inquisition), Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
+          <t>Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, The Inquisition), Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable, Infused Knowledge.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable, Infused Knowledge.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best-Craftsmanship Hellpistol, Common-Craftsmanship Boltgun, Xeno-mesh Armour (AP 2), Inquisitorial Seal/Rosette (hidden), Autoquill, Dataslate, Multikey, Synskin, Cameleoline Cloak. Secret (GM Only): Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction. Favour Owed: Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
+          <t>Best-Craftsmanship Hellpistol, Common-Craftsmanship Boltgun, Xeno-mesh Armour (AP 2), Inquisitorial Seal/Rosette (hidden), Autoquill, Dataslate, Multikey, Synskin, Cameleoline Cloak. Secret (GM Only): Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction. Favour Owed: Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction.</t>
+          <t>Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
+          <t>Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Untouchable Witch Finder</t>
+          <t>The Untouchable Witch Finder</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneschal (Alternate Rank: Witch Finder) + Untouchable Package</t>
+          <t>Seneschal (Alternate Rank: Witch Finder) + Untouchable Package</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anti-psyker investigator and inquisitorial liaison who passively disrupts Warp energy and nullifies psychic powers.</t>
+          <t>Anti-psyker investigator and inquisitorial liaison who passively disrupts Warp energy and nullifies psychic powers.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imperial World</t>
+          <t>Imperial World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scapegrace</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Press-Ganged</t>
+          <t>Press-Ganged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vengeance</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneschal</t>
+          <t>Seneschal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal: Wanted Fugitive</t>
+          <t>Criminal: Wanted Fugitive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Untouchable (1): Completely immune to direct psychic powers; degrades Psy Rating of all nearby psychic manifestations by 1.; Seeker of Lore: Spend a Fate Point to automatically succeed on Lore, Ciphers, or Logic tests in minimum time.</t>
+          <t>Untouchable (1): Completely immune to direct psychic powers; degrades Psy Rating of all nearby psychic manifestations by 1.; Seeker of Lore: Spend a Fate Point to automatically succeed on Lore, Ciphers, or Logic tests in minimum time.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barter, Commerce, Common Lore (Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, Psykers), Inquiry, Interrogation, Literacy, Psyniscience, Scrutiny, Security, Silent Move.</t>
+          <t>Barter, Commerce, Common Lore (Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, Psykers), Inquiry, Interrogation, Literacy, Psyniscience, Scrutiny, Security, Silent Move.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Exotic Weapon Training (Web Pistol), Mind Sight, Resistance (Psychic Powers), Hatred (Psykers), Disarm.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Exotic Weapon Training (Web Pistol), Mind Sight, Resistance (Psychic Powers), Hatred (Psykers), Disarm.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
+          <t>Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
+          <t>Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
+          <t>Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Heretek Tech-Acolyte</t>
+          <t>The Heretek Tech-Acolyte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explorator (Alternate Rank: Acolyte of Abraxas)</t>
+          <t>Explorator (Alternate Rank: Acolyte of Abraxas)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archeotech specialist who integrates psychically active alien relics into his cyber-mantle to wield Warp-tech abilities.</t>
+          <t>Archeotech specialist who integrates psychically active alien relics into his cyber-mantle to wield Warp-tech abilities.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forge World</t>
+          <t>Forge World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savant</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renegade</t>
+          <t>Renegade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dark Voyage</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endurance</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explorator</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renegade: Dark Visionary</t>
+          <t>Renegade: Dark Visionary</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unhallowed Discovery: Integrates a psychically active xenos artifact into his cyber-mantle, gaining Psy Rating 1 and access to a psychic technique.; Explorator Implants: Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics.</t>
+          <t>Unhallowed Discovery: Integrates a psychically active xenos artifact into his cyber-mantle, gaining Psy Rating 1 and access to a psychic technique.; Explorator Implants: Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Medicae, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Tech-Use (+10), Trade (Archaeologist, Technomat).</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Medicae, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Tech-Use (+10), Trade (Archaeologist, Technomat).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Unhallowed Discovery, Autosanguine, Technical Knock, Enemy (Adeptus Mechanicus).</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Unhallowed Discovery, Autosanguine, Technical Knock, Enemy (Adeptus Mechanicus).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrated Psychically-Charged Xenos Artifact, Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace Armour, Multikey, Combi-tool, Sacred Unguents, Servo-skull. Secret (GM Only): Receives non-human telepathic feedback from the alien artifact embedded directly in his spine. Favour Owed: Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
+          <t>Integrated Psychically-Charged Xenos Artifact, Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace Armour, Multikey, Combi-tool, Sacred Unguents, Servo-skull. Secret (GM Only): Receives non-human telepathic feedback from the alien artifact embedded directly in his spine. Favour Owed: Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Receives non-human telepathic feedback from the alien artifact embedded directly in his spine.</t>
+          <t>Receives non-human telepathic feedback from the alien artifact embedded directly in his spine.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
+          <t>Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Exiled House Visscher Navigator</t>
+          <t>The Exiled House Visscher Navigator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator (Magisterial House: House Visscher)</t>
+          <t>Navigator (Magisterial House: House Visscher)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Warp guide who uses blood-ripple divination rituals and extensive contacts to navigate uncharted routes in the Expanse.</t>
+          <t>Master Warp guide who uses blood-ripple divination rituals and extensive contacts to navigate uncharted routes in the Expanse.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Void Born</t>
+          <t>Void Born</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scapegrace</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ship-Lorn</t>
+          <t>Ship-Lorn</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestige</t>
+          <t>Prestige</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound: Duty to Dynasty</t>
+          <t>Duty Bound: Duty to Dynasty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">House Visscher Lineage: Grants Extensive Contacts and A Tangled Web interaction modifiers.; Blood-Ripple Divination Ritual: Adds +2d10 to Psyniscience Tests when divining auguries for a Warp route.; Warp Eye: Access to Navigator Powers (The Lidless Stare, Seek the Path).; Access to Navigator Powers (The Lidless Stare, Seek the Path).</t>
+          <t>House Visscher Lineage: Grants Extensive Contacts and A Tangled Web interaction modifiers.; Blood-Ripple Divination Ritual: Adds +2d10 to Psyniscience Tests when divining auguries for a Warp route.; Warp Eye: Access to Navigator Powers (The Lidless Stare, Seek the Path).; Access to Navigator Powers (The Lidless Stare, Seek the Path).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (Imperial Navy, Navis Nobilite), Forbidden Lore (Navigators, Warp), Literacy, Navigation (Stellar, Warp), Psyniscience, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Trade (Astrographer).</t>
+          <t>Common Lore (Imperial Navy, Navis Nobilite), Forbidden Lore (Navigators, Warp), Literacy, Navigation (Stellar, Warp), Psyniscience, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Trade (Astrographer).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator, Pistol Weapon Training (Universal), Peer (Ma'Kao Dynasty), Good Reputation (House Cassini), Rival (House Ortellius), Rival (Winterscale Dynasty).</t>
+          <t>Navigator, Pistol Weapon Training (Universal), Peer (Ma'Kao Dynasty), Good Reputation (House Cassini), Rival (House Ortellius), Rival (Winterscale Dynasty).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour, Emperor's Tarot Deck, Silk Headscarf, Nobilite Robes. Secret (GM Only): Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
+          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour, Emperor's Tarot Deck, Silk Headscarf, Nobilite Robes. Secret (GM Only): Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift.</t>
+          <t>Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
+          <t>Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Beast-Master Privateer</t>
+          <t>The Beast-Master Privateer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Void-Master (Alternate Rank: Beastmaster)</t>
+          <t>Void-Master (Alternate Rank: Beastmaster)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small craft pilot and beast tamer who commands bonded wild predators to assist in boarding actions and scouting.</t>
+          <t>Small craft pilot and beast tamer who commands bonded wild predators to assist in boarding actions and scouting.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Death World</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scavenger</t>
+          <t>Scavenger</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calamity</t>
+          <t>Calamity</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endurance</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Void-Master</t>
+          <t>Void-Master</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal: Hunted by Crime Baron</t>
+          <t>Criminal: Hunted by Crime Baron</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastery of Small Craft: Re-roll all failed Pilot Tests with shuttles, heavy lifters, guncutters, and starfighters.; Bestial Minion: Commands a bonded, tamed wild beast or cyber-construct.</t>
+          <t>Mastery of Small Craft: Re-roll all failed Pilot Tests with shuttles, heavy lifters, guncutters, and starfighters.; Bestial Minion: Commands a bonded, tamed wild beast or cyber-construct.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awareness, Common Lore (Imperial Navy, War), Dodge, Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
+          <t>Awareness, Common Lore (Imperial Navy, War), Dodge, Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Nerves of Steel, Bestial Minion, Coordinated Strike, Hardy.</t>
+          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Nerves of Steel, Bestial Minion, Coordinated Strike, Hardy.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tamed Attack Squig / Bestial Minion, Hand Cannon, Best-Craftsmanship Mono-sword, Guard Flak Armour, Micro-bead, Void Suit, Re-breather. Secret (GM Only): His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy. Favour Owed: Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
+          <t>Tamed Attack Squig / Bestial Minion, Hand Cannon, Best-Craftsmanship Mono-sword, Guard Flak Armour, Micro-bead, Void Suit, Re-breather. Secret (GM Only): His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy. Favour Owed: Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy.</t>
+          <t>His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
+          <t>Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanctioned Psyker</t>
+          <t>Sanctioned Psyker</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanctioned Combat Psyker (Dark Heresy 5,000 XP Conversion / Biomancer-Pyromancer)</t>
+          <t>Sanctioned Combat Psyker (Dark Heresy 5,000 XP Conversion / Biomancer-Pyromancer)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heavy fire support and biological enhancer; handles warp-tainted threats that conventional weaponry cannot reach.</t>
+          <t>Heavy fire support and biological enhancer; handles warp-tainted threats that conventional weaponry cannot reach.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mind-Cleansed/Imperial World</t>
+          <t>Mind-Cleansed/Imperial World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Child of the Creed</t>
+          <t>Child of the Creed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tainted</t>
+          <t>Tainted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dark Voyage</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortune</t>
+          <t>Fortune</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astropath Transcendent / Psyker Import</t>
+          <t>Astropath Transcendent / Psyker Import</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tainted: Deviant Philosophy</t>
+          <t>Tainted: Deviant Philosophy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanctioned Psyker (Reduced chance of triggering severe Perils of the Warp compared to unsanctioned psykers).</t>
+          <t>Sanctioned Psyker (Reduced chance of triggering severe Perils of the Warp compared to unsanctioned psykers).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biomancy: Bio-healing (heal wounds/fatigue), Iron Arm (boost Strength and Toughness). Pyromancy: Spontaneous Combustion (ignite targets at range), Fire Shield (deflective thermal barrier).</t>
+          <t>Biomancy: Bio-healing (heal wounds/fatigue), Iron Arm (boost Strength and Toughness). Pyromancy: Spontaneous Combustion (ignite targets at range), Fire Shield (deflective thermal barrier).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awareness, Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Speak Language (High Gothic, Low Gothic).</t>
+          <t>Awareness, Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Psy Rating 3, Resistance (Psychic Powers), Strong Minded, Unshakeable Faith, Warp Sense.</t>
+          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Psy Rating 3, Resistance (Psychic Powers), Strong Minded, Unshakeable Faith, Warp Sense.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good-Craftsmanship Stub Automatic, Force Sword (or Shock Staff), Flak Vest (AP 3), Psy-Focus, Sanctified Charm, Vox-Microbead, 3 doses of Stimm. Secret (GM Only): Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning. Favour Owed: Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
+          <t>Good-Craftsmanship Stub Automatic, Force Sword (or Shock Staff), Flak Vest (AP 3), Psy-Focus, Sanctified Charm, Vox-Microbead, 3 doses of Stimm. Secret (GM Only): Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning. Favour Owed: Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning.</t>
+          <t>Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
+          <t>Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aeldari Corsair</t>
+          <t>Aeldari Corsair</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eldar Corsair (Into the Storm Supplement)</t>
+          <t>Eldar Corsair (Into the Storm Supplement)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scout, void-skirmisher, and high-speed assault vanguard.</t>
+          <t>Scout, void-skirmisher, and high-speed assault vanguard.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aeldari</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eldar Corsair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alien Physiology: Human medicae tools/tests suffer a -20 penalty when used on an Aeldari.; Waystone (Soul Stone): Protects the character's soul upon death from being consumed by She Who Thirsts.</t>
+          <t>Alien Physiology: Human medicae tools/tests suffer a -20 penalty when used on an Aeldari.; Waystone (Soul Stone): Protects the character's soul upon death from being consumed by She Who Thirsts.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans).</t>
+          <t>Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Pilot (Personal / Jump Pack), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
+          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Pilot (Personal / Jump Pack), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catfall, Leap Up, Swift Attack, Ambidextrous, Two-Weapon Wielder (Melee/Ballistic), Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
+          <t>Catfall, Leap Up, Swift Attack, Ambidextrous, Two-Weapon Wielder (Melee/Ballistic), Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shuriken Pistol, Eldar Power Sword, Aeldari Mesh Armour (AP 3), Waystone, Eldar Jump Pack or Cameleoline Cloak. Secret (GM Only): Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
+          <t>Shuriken Pistol, Eldar Power Sword, Aeldari Mesh Armour (AP 3), Waystone, Eldar Jump Pack or Cameleoline Cloak. Secret (GM Only): Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council.</t>
+          <t>Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
+          <t>Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Swashbuckling Dynasty Heir</t>
+          <t>The Swashbuckling Dynasty Heir</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rogue Trader</t>
+          <t>Rogue Trader</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A charismatic, front-line duelist who leads expeditions from the front rather than from the safety of the flagship bridge.</t>
+          <t>A charismatic, front-line duelist who leads expeditions from the front rather than from the safety of the flagship bridge.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serves as the tactical linchpin. Uses high Fellowship and Command to manipulate the Space Hulk Alert Level, direct Hostile AI targets, and generate extra Momentum Pool points for the party.</t>
+          <t>Serves as the tactical linchpin. Uses high Fellowship and Command to manipulate the Space Hulk Alert Level, direct Hostile AI targets, and generate extra Momentum Pool points for the party.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7,500 XP (Unique Rogue Trader)</t>
+          <t>7,500 XP (Unique Rogue Trader)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noble Born</t>
+          <t>Noble Born</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaunted</t>
+          <t>Vaunted</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">High Vendetta</t>
+          <t>High Vendetta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renown</t>
+          <t>Renown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rogue Trader</t>
+          <t>Rogue Trader</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound: Duty to Dynasty</t>
+          <t>Duty Bound: Duty to Dynasty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exceptional Leader (Free Action once per round: Grant an ally within sight/hearing +10% to any one test).</t>
+          <t>Exceptional Leader (Free Action once per round: Grant an ally within sight/hearing +10% to any one test).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Command, Commerce, Charm, Evaluate, Literacy, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Inquiry, Dodge.</t>
+          <t>Command, Commerce, Charm, Evaluate, Literacy, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Inquiry, Dodge.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Air of Authority, Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Renowned Warrant, Peer (Nobility), Decadence.</t>
+          <t>Air of Authority, Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Renowned Warrant, Peer (Nobility), Decadence.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common-Craftsmanship Plasma Pistol, Best-Craftsmanship Power Sword, Enforcer Light Carapace (AP 5), Xeno-pelt Cloak, Fine Clothing, Micro-bead. Secret (GM Only): The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago. Favour Owed: Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
+          <t>Common-Craftsmanship Plasma Pistol, Best-Craftsmanship Power Sword, Enforcer Light Carapace (AP 5), Xeno-pelt Cloak, Fine Clothing, Micro-bead. Secret (GM Only): The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago. Favour Owed: Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago.</t>
+          <t>The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
+          <t>Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Archeotech Sanctifier</t>
+          <t>The Archeotech Sanctifier</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explorator</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">An inquisitive Mechanicus Magos-Explorator who views megastructures as holy cathedrals of the Omnissiah awaiting sanctification.</t>
+          <t>An inquisitive Mechanicus Magos-Explorator who views megastructures as holy cathedrals of the Omnissiah awaiting sanctification.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primary utility specialist. Critical for opening locked/sealed bulkheads, disarming plasma/environmental hazard tiles, and converting Archeotech Discovery Cards into permanent Dynasty Profit Factor.</t>
+          <t>Primary utility specialist. Critical for opening locked/sealed bulkheads, disarming plasma/environmental hazard tiles, and converting Archeotech Discovery Cards into permanent Dynasty Profit Factor.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forge World</t>
+          <t>Forge World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savant</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renegade</t>
+          <t>Renegade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calamity</t>
+          <t>Calamity</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endurance</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explorator</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renegade: Free-Thinker</t>
+          <t>Renegade: Free-Thinker</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explorator Implants (Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics).</t>
+          <t>Explorator Implants (Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Tech-Use (+10), Logic, Trade (Technomat), Medicae, Security, Awareness.</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Tech-Use (+10), Logic, Trade (Technomat), Medicae, Security, Awareness.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Technical Knock, Autosanguine, Nerves of Steel, Light Sleeper.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Technical Knock, Autosanguine, Nerves of Steel, Light Sleeper.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace (AP 5), Servo-Skull Familiar, Combi-tool, Multikey, Sacred Unguents. Secret (GM Only): Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence. Favour Owed: Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
+          <t>Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace (AP 5), Servo-Skull Familiar, Combi-tool, Multikey, Sacred Unguents. Secret (GM Only): Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence. Favour Owed: Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence.</t>
+          <t>Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
+          <t>Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Void-Breacher Veteran</t>
+          <t>The Void-Breacher Veteran</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arch-Militant</t>
+          <t>Arch-Militant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A hardened, scarred ex-Naval Armsman specializing in close-quarters boarding actions, hallway breaches, and point-blank crowd control.</t>
+          <t>A hardened, scarred ex-Naval Armsman specializing in close-quarters boarding actions, hallway breaches, and point-blank crowd control.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front-line tank and hallway anchor. Holds narrow corridors against waves of hostiles.</t>
+          <t>Front-line tank and hallway anchor. Holds narrow corridors against waves of hostiles.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Death World</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubjack</t>
+          <t>Stubjack</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hand of War</t>
+          <t>The Hand of War</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vengeance</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arch-Militant</t>
+          <t>Arch-Militant</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criminal: Wanted Fugitive</t>
+          <t>Criminal: Wanted Fugitive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Master (+10% to hit, +2 Damage, and +2 Initiative when using weapons of a chosen class, e.g., Basic/Shotguns or Flamers).</t>
+          <t>Weapon Master (+10% to hit, +2 Damage, and +2 Initiative when using weapons of a chosen class, e.g., Basic/Shotguns or Flamers).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (War), Dodge, Intimidate (+10), Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
+          <t>Common Lore (War), Dodge, Intimidate (+10), Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Hatred (Pirates/Mutants), Sound Constitution, Bulging Biceps.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Hatred (Pirates/Mutants), Sound Constitution, Bulging Biceps.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naval Shotcannon (or Good-Craftsmanship Hellgun), Mono-edged Boarding Cutlass, Enforcer Light Carapace (AP 5), Micro-bead, Stimm (3 doses), Manacles. Secret (GM Only): Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity. Favour Owed: Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
+          <t>Naval Shotcannon (or Good-Craftsmanship Hellgun), Mono-edged Boarding Cutlass, Enforcer Light Carapace (AP 5), Micro-bead, Stimm (3 doses), Manacles. Secret (GM Only): Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity. Favour Owed: Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity.</t>
+          <t>Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
+          <t>Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Void-Eye Scion</t>
+          <t>The Void-Eye Scion</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A noble-born mutant whose Warp Eye sees both the tides of the Immaterium and the latent warp-bleeds of precursor architecture.</t>
+          <t>A noble-born mutant whose Warp Eye sees both the tides of the Immaterium and the latent warp-bleeds of precursor architecture.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scout and crowd-controller. Uses Psyniscience to scout unopened tiles through bulkheads and fires the Lidless Stare down choke points.</t>
+          <t>Scout and crowd-controller. Uses Psyniscience to scout unopened tiles through bulkheads and fires the Lidless Stare down choke points.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Void Born</t>
+          <t>Void Born</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scapegrace</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen by Destiny</t>
+          <t>Chosen by Destiny</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dark Voyage</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pride</t>
+          <t>Pride</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen by Destiny: Seeker of Truth</t>
+          <t>Chosen by Destiny: Seeker of Truth</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warp Eye: Grants access to Navigator Powers (starts with The Lidless Stare).; Shipwise &amp; Void Accustomed: Immune to space travel sickness; zero-G is not treated as difficult terrain.; Grants access to Navigator Powers (starts with The Lidless Stare).</t>
+          <t>Warp Eye: Grants access to Navigator Powers (starts with The Lidless Stare).; Shipwise &amp; Void Accustomed: Immune to space travel sickness; zero-G is not treated as difficult terrain.; Grants access to Navigator Powers (starts with The Lidless Stare).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Psyniscience (+10), Scholastic Lore (Astromancy), Awareness.</t>
+          <t>Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Psyniscience (+10), Scholastic Lore (Astromancy), Awareness.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator, Pistol Weapon Training (Universal), Foresight, Resistance (Fear), Dark Soul, Warp Sense.</t>
+          <t>Navigator, Pistol Weapon Training (Universal), Foresight, Resistance (Fear), Dark Soul, Warp Sense.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour (AP 3), Nobilite Robes, Silk Headscarf/Blindfold, Emperor's Tarot Deck. Secret (GM Only): Navigator mutations are accelerating beyond house-sanctioned parameters. Favour Owed: Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
+          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour (AP 3), Nobilite Robes, Silk Headscarf/Blindfold, Emperor's Tarot Deck. Secret (GM Only): Navigator mutations are accelerating beyond house-sanctioned parameters. Favour Owed: Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navigator mutations are accelerating beyond house-sanctioned parameters.</t>
+          <t>Navigator mutations are accelerating beyond house-sanctioned parameters.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
+          <t>Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Ork Waaagh!-Shaman</t>
+          <t>The Ork Waaagh!-Shaman</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ork Weirdboy Career Path</t>
+          <t>Ork Weirdboy Career Path</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xenos Battle Psyker and Void Navigator.</t>
+          <t>Xenos Battle Psyker and Void Navigator.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Da Power of Waaagh!: Gains Psy Rating bonuses from nearby Orks; rolls on the Weird Fings and 'Eadbang tables instead of standard Psychic Phenomena.; Throo Da Kosmos: Navigates the Warp by instinct using Survival in place of Navigation (Warp).</t>
+          <t>Da Power of Waaagh!: Gains Psy Rating bonuses from nearby Orks; rolls on the Weird Fings and 'Eadbang tables instead of standard Psychic Phenomena.; Throo Da Kosmos: Navigates the Warp by instinct using Survival in place of Navigation (Warp).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orkoid Physiology (Unnatural Toughness (x2), Sturdy, Iron Jaw, True Grit).</t>
+          <t>Orkoid Physiology (Unnatural Toughness (x2), Sturdy, Iron Jaw, True Grit).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awareness, Common Lore (Orks, War), Psyniscience, Speak Language (Low Gothic, Ork), Survival.</t>
+          <t>Awareness, Common Lore (Orks, War), Psyniscience, Speak Language (Low Gothic, Ork), Survival.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy Rating 2, Da Power of Waaagh!, Throo Da Kosmos, Minderz, Peer (Own Clan), Xenos Weapon Training (Ork).</t>
+          <t>Psy Rating 2, Da Power of Waaagh!, Throo Da Kosmos, Minderz, Peer (Own Clan), Xenos Weapon Training (Ork).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copper channelling rod, Squig-hide coat and leggings, Choppa, Slugga, 2 Minderz bodyguards. Secret (GM Only): Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team. Favour Owed: Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
+          <t>Copper channelling rod, Squig-hide coat and leggings, Choppa, Slugga, 2 Minderz bodyguards. Secret (GM Only): Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team. Favour Owed: Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team.</t>
+          <t>Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
+          <t>Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — IDENTITY —</t>
+          <t># — IDENTITY —</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Red Consecrator</t>
+          <t>The Red Consecrator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missionary (Alternate Rank: Red Consecrator)</t>
+          <t>Missionary (Alternate Rank: Red Consecrator)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role in crew</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martial zealot and front-line shock trooper who treats melee combat as a form of sacred worship.</t>
+          <t>Martial zealot and front-line shock trooper who treats melee combat as a form of sacred worship.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">XP total</t>
+          <t>XP total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait URL</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ORIGIN PATH —</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank where the character has none (xenos)</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home World</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Death World</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birthright</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubjack</t>
+          <t>Stubjack</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lure of the Void</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trials</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hand of War</t>
+          <t>The Hand of War</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vengeance</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Career (origin step)</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missionary</t>
+          <t>Missionary</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin path choices</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duty Bound: Duty to Humanity; Missionary: Red Consecrator Alt Rank</t>
+          <t>Duty Bound: Duty to Humanity; Missionary: Red Consecrator Alt Rank</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — FINAL CHARACTERISTICS —</t>
+          <t># — FINAL CHARACTERISTICS —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already include origin modifiers and advances — do NOT reapply</t>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>Weapon Skill</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballistic Skill</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>Ballistic Skill</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strength</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toughness</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agility</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelligence</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perception</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>Perception</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willpower</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fellowship</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — DERIVED —</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final wounds</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final fate points</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psy rating</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — ABILITIES —</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Special ability</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pure Faith: Immune to Daemonic Presence; can spend or burn Fate Points to resist Warp corruption and inspire allies.; Rage of the Zealot: Inflicts Righteous Fury on a result of 9 or 10 when attacking hated foes with melee weapons.</t>
+          <t>Pure Faith: Immune to Daemonic Presence; can spend or burn Fate Points to resist Warp corruption and inspire allies.; Rage of the Zealot: Inflicts Righteous Fury on a result of 9 or 10 when attacking hated foes with melee weapons.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin / trait modifiers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychic powers</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — SKILLS, TALENTS, WARGEAR —</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">semicolon separated</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skills</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Lore (Imperial Creed, Imperium, War), Command, Dodge, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
+          <t>Common Lore (Imperial Creed, Imperium, War), Command, Dodge, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talents</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Hatred (Psykers), Hatred (Mutants), Litany of Hate, Rage of the Zealot.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Hatred (Psykers), Hatred (Mutants), Litany of Hate, Rage of the Zealot.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wargear</t>
+          <t>Wargear</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eviscerator two-handed chainsword, Flamer, Guard Flak Armour, Ecclesiarchal Robes, Aquila Pendant, Micro-bead. Secret (GM Only): Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities. Favour Owed: Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
+          <t>Eviscerator two-handed chainsword, Flamer, Guard Flak Armour, Ecclesiarchal Robes, Aquila Pendant, Micro-bead. Secret (GM Only): Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities. Favour Owed: Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"># — GM —</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secret</t>
+          <t>Secret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities.</t>
+          <t>Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favour owed</t>
+          <t>Favour owed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
+          <t>Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/characters.xlsx
+++ b/characters.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -461,396 +461,403 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Seneschal (Inquisitorial Representative)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Seneschal (Inquisitorial Representative)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Spymaster, political liaison, and covert handler ensuring the Rogue Trader's dynasty remains compliant with Imperial law.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Spymaster, political liaison, and covert handler ensuring the Rogue Trader's dynasty remains compliant with Imperial law.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Imperial World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>Imperial World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duty Bound</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>High Vendetta</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prestige</t>
+          <t>High Vendetta</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seneschal</t>
+          <t>Prestige</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duty Bound: Duty to the Throne</t>
+          <t>Seneschal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Duty Bound: Duty to the Throne</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>32</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Seeker of Lore (Spend a Fate Point to automatically succeed at any Ciphers, Lore, or Logic test in minimum time; +1 bonus Degree of Success on Commerce, Inquiry, or Evaluate tests).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Seeker of Lore (Spend a Fate Point to automatically succeed at any Ciphers, Lore, or Logic test in minimum time; +1 bonus Degree of Success on Commerce, Inquiry, or Evaluate tests).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, The Inquisition), Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable, Infused Knowledge.</t>
+          <t>Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, The Inquisition), Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Best-Craftsmanship Hellpistol, Common-Craftsmanship Boltgun, Xeno-mesh Armour (AP 2), Inquisitorial Seal/Rosette (hidden), Autoquill, Dataslate, Multikey, Synskin, Cameleoline Cloak. Secret (GM Only): Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction. Favour Owed: Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable, Infused Knowledge.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best-Craftsmanship Hellpistol, Common-Craftsmanship Boltgun, Xeno-mesh Armour (AP 2), Inquisitorial Seal/Rosette (hidden), Autoquill, Dataslate, Multikey, Synskin, Cameleoline Cloak. Secret (GM Only): Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction. Favour Owed: Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Transmits encrypted reports regarding the dynasty’s archeotech recovery back to a radical Inquisitorial faction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Void-Breacher Veteran (Arch-Militant) for extracting them during an unexpected hive station lockdown.</t>
         </is>
@@ -867,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -908,396 +915,403 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Seneschal (Alternate Rank: Witch Finder) + Untouchable Package</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Seneschal (Alternate Rank: Witch Finder) + Untouchable Package</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Anti-psyker investigator and inquisitorial liaison who passively disrupts Warp energy and nullifies psychic powers.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Anti-psyker investigator and inquisitorial liaison who passively disrupts Warp energy and nullifies psychic powers.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Imperial World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scapegrace</t>
+          <t>Imperial World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Criminal</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Press-Ganged</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vengeance</t>
+          <t>Press-Ganged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seneschal</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Criminal: Wanted Fugitive</t>
+          <t>Seneschal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Criminal: Wanted Fugitive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>35</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Untouchable (1): Completely immune to direct psychic powers; degrades Psy Rating of all nearby psychic manifestations by 1.; Seeker of Lore: Spend a Fate Point to automatically succeed on Lore, Ciphers, or Logic tests in minimum time.</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Untouchable (1): Completely immune to direct psychic powers; degrades Psy Rating of all nearby psychic manifestations by 1.; Seeker of Lore: Spend a Fate Point to automatically succeed on Lore, Ciphers, or Logic tests in minimum time.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Barter, Commerce, Common Lore (Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, Psykers), Inquiry, Interrogation, Literacy, Psyniscience, Scrutiny, Security, Silent Move.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Exotic Weapon Training (Web Pistol), Mind Sight, Resistance (Psychic Powers), Hatred (Psykers), Disarm.</t>
+          <t>Barter, Commerce, Common Lore (Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, Psykers), Inquiry, Interrogation, Literacy, Psyniscience, Scrutiny, Security, Silent Move.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Exotic Weapon Training (Web Pistol), Mind Sight, Resistance (Psychic Powers), Hatred (Psykers), Disarm.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
@@ -1314,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1355,401 +1369,408 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Explorator (Alternate Rank: Acolyte of Abraxas)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Explorator (Alternate Rank: Acolyte of Abraxas)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Archeotech specialist who integrates psychically active alien relics into his cyber-mantle to wield Warp-tech abilities.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Archeotech specialist who integrates psychically active alien relics into his cyber-mantle to wield Warp-tech abilities.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Forge World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>Forge World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Renegade</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dark Voyage</t>
+          <t>Renegade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Endurance</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Explorator</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Renegade: Dark Visionary</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Renegade: Dark Visionary</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>32</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Unhallowed Discovery: Integrates a psychically active xenos artifact into his cyber-mantle, gaining Psy Rating 1 and access to a psychic technique.; Explorator Implants: Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics.</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unhallowed Discovery: Integrates a psychically active xenos artifact into his cyber-mantle, gaining Psy Rating 1 and access to a psychic technique.; Explorator Implants: Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Medicae, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Tech-Use (+10), Trade (Archaeologist, Technomat).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Unhallowed Discovery, Autosanguine, Technical Knock, Enemy (Adeptus Mechanicus).</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Medicae, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Tech-Use (+10), Trade (Archaeologist, Technomat).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Integrated Psychically-Charged Xenos Artifact, Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace Armour, Multikey, Combi-tool, Sacred Unguents, Servo-skull. Secret (GM Only): Receives non-human telepathic feedback from the alien artifact embedded directly in his spine. Favour Owed: Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Unhallowed Discovery, Autosanguine, Technical Knock, Enemy (Adeptus Mechanicus).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Integrated Psychically-Charged Xenos Artifact, Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace Armour, Multikey, Combi-tool, Sacred Unguents, Servo-skull. Secret (GM Only): Receives non-human telepathic feedback from the alien artifact embedded directly in his spine. Favour Owed: Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Receives non-human telepathic feedback from the alien artifact embedded directly in his spine.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Receives non-human telepathic feedback from the alien artifact embedded directly in his spine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Archeotech Sanctifier (Explorator) for diverting an Imperial Tech-Heresy audit away from his workstation.</t>
         </is>
@@ -1766,7 +1787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1807,396 +1828,403 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Navigator (Magisterial House: House Visscher)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Navigator (Magisterial House: House Visscher)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Master Warp guide who uses blood-ripple divination rituals and extensive contacts to navigate uncharted routes in the Expanse.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Master Warp guide who uses blood-ripple divination rituals and extensive contacts to navigate uncharted routes in the Expanse.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Void Born</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scapegrace</t>
+          <t>Void Born</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duty Bound</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ship-Lorn</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prestige</t>
+          <t>Ship-Lorn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Prestige</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duty Bound: Duty to Dynasty</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Duty Bound: Duty to Dynasty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>26</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>House Visscher Lineage: Grants Extensive Contacts and A Tangled Web interaction modifiers.; Blood-Ripple Divination Ritual: Adds +2d10 to Psyniscience Tests when divining auguries for a Warp route.; Warp Eye: Access to Navigator Powers (The Lidless Stare, Seek the Path).; Access to Navigator Powers (The Lidless Stare, Seek the Path).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>House Visscher Lineage: Grants Extensive Contacts and A Tangled Web interaction modifiers.; Blood-Ripple Divination Ritual: Adds +2d10 to Psyniscience Tests when divining auguries for a Warp route.; Warp Eye: Access to Navigator Powers (The Lidless Stare, Seek the Path).; Access to Navigator Powers (The Lidless Stare, Seek the Path).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (Imperial Navy, Navis Nobilite), Forbidden Lore (Navigators, Warp), Literacy, Navigation (Stellar, Warp), Psyniscience, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Trade (Astrographer).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Navigator, Pistol Weapon Training (Universal), Peer (Ma'Kao Dynasty), Good Reputation (House Cassini), Rival (House Ortellius), Rival (Winterscale Dynasty).</t>
+          <t>Common Lore (Imperial Navy, Navis Nobilite), Forbidden Lore (Navigators, Warp), Literacy, Navigation (Stellar, Warp), Psyniscience, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Trade (Astrographer).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour, Emperor's Tarot Deck, Silk Headscarf, Nobilite Robes. Secret (GM Only): Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
+          <t>Navigator, Pistol Weapon Training (Universal), Peer (Ma'Kao Dynasty), Good Reputation (House Cassini), Rival (House Ortellius), Rival (Winterscale Dynasty).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour, Emperor's Tarot Deck, Silk Headscarf, Nobilite Robes. Secret (GM Only): Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Exile from House Visscher was caused by deliberately misguiding a rival noble family's transport into a warp rift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Swashbuckling Dynasty Heir (Rogue Trader) for granting asylum and passage beyond Imperial sector borders.</t>
         </is>
@@ -2213,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2254,396 +2282,403 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Void-Master (Alternate Rank: Beastmaster)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Void-Master (Alternate Rank: Beastmaster)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Small craft pilot and beast tamer who commands bonded wild predators to assist in boarding actions and scouting.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Small craft pilot and beast tamer who commands bonded wild predators to assist in boarding actions and scouting.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Death World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scavenger</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Criminal</t>
+          <t>Scavenger</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calamity</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Endurance</t>
+          <t>Calamity</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Void-Master</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Criminal: Hunted by Crime Baron</t>
+          <t>Void-Master</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Criminal: Hunted by Crime Baron</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>38</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mastery of Small Craft: Re-roll all failed Pilot Tests with shuttles, heavy lifters, guncutters, and starfighters.; Bestial Minion: Commands a bonded, tamed wild beast or cyber-construct.</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mastery of Small Craft: Re-roll all failed Pilot Tests with shuttles, heavy lifters, guncutters, and starfighters.; Bestial Minion: Commands a bonded, tamed wild beast or cyber-construct.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Awareness, Common Lore (Imperial Navy, War), Dodge, Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Nerves of Steel, Bestial Minion, Coordinated Strike, Hardy.</t>
+          <t>Awareness, Common Lore (Imperial Navy, War), Dodge, Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tamed Attack Squig / Bestial Minion, Hand Cannon, Best-Craftsmanship Mono-sword, Guard Flak Armour, Micro-bead, Void Suit, Re-breather. Secret (GM Only): His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy. Favour Owed: Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
+          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Nerves of Steel, Bestial Minion, Coordinated Strike, Hardy.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tamed Attack Squig / Bestial Minion, Hand Cannon, Best-Craftsmanship Mono-sword, Guard Flak Armour, Micro-bead, Void Suit, Re-breather. Secret (GM Only): His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy. Favour Owed: Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>His primary combat beast is an illegal, bio-engineered xenos lifeform classified as dangerous by the Imperial Navy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Aeldari Corsair for instruction in tracking xenos fauna across death worlds.</t>
         </is>
@@ -2660,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2701,286 +2736,281 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sanctioned Combat Psyker (Dark Heresy 5,000 XP Conversion / Biomancer-Pyromancer)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sanctioned Combat Psyker (Dark Heresy 5,000 XP Conversion / Biomancer-Pyromancer)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Heavy fire support and biological enhancer; handles warp-tainted threats that conventional weaponry cannot reach.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Heavy fire support and biological enhancer; handles warp-tainted threats that conventional weaponry cannot reach.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mind-Cleansed/Imperial World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Child of the Creed</t>
+          <t>Mind-Cleansed/Imperial World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tainted</t>
+          <t>Child of the Creed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dark Voyage</t>
+          <t>Tainted</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fortune</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Astropath Transcendent / Psyker Import</t>
+          <t>Fortune</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tainted: Deviant Philosophy</t>
+          <t>Astropath Transcendent / Psyker Import</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Tainted: Deviant Philosophy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>28</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2992,115 +3022,127 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sanctioned Psyker (Reduced chance of triggering severe Perils of the Warp compared to unsanctioned psykers).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sanctioned Psyker (Reduced chance of triggering severe Perils of the Warp compared to unsanctioned psykers).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Biomancy: Bio-healing (heal wounds/fatigue), Iron Arm (boost Strength and Toughness). Pyromancy: Spontaneous Combustion (ignite targets at range), Fire Shield (deflective thermal barrier).</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
+          <t>Psychic powers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>semicolon separated</t>
+          <t>Biomancy: Bio-healing (heal wounds/fatigue), Iron Arm (boost Strength and Toughness). Pyromancy: Spontaneous Combustion (ignite targets at range), Fire Shield (deflective thermal barrier).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Awareness, Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Speak Language (High Gothic, Low Gothic).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Psy Rating 3, Resistance (Psychic Powers), Strong Minded, Unshakeable Faith, Warp Sense.</t>
+          <t>Awareness, Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Good-Craftsmanship Stub Automatic, Force Sword (or Shock Staff), Flak Vest (AP 3), Psy-Focus, Sanctified Charm, Vox-Microbead, 3 doses of Stimm. Secret (GM Only): Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning. Favour Owed: Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
+          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Psy Rating 3, Resistance (Psychic Powers), Strong Minded, Unshakeable Faith, Warp Sense.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Good-Craftsmanship Stub Automatic, Force Sword (or Shock Staff), Flak Vest (AP 3), Psy-Focus, Sanctified Charm, Vox-Microbead, 3 doses of Stimm. Secret (GM Only): Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning. Favour Owed: Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Experiences unsanctioned visions from a Warp entity that were left behind during incomplete sanctioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Void-Eye Scion (Navigator) for masking their warp signatures during a high-stress warp leap.</t>
         </is>
@@ -3117,7 +3159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3158,376 +3200,383 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eldar Corsair (Into the Storm Supplement)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eldar Corsair (Into the Storm Supplement)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Scout, void-skirmisher, and high-speed assault vanguard.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Scout, void-skirmisher, and high-speed assault vanguard.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aeldari</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aeldari</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Eldar Corsair</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Eldar Corsair</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Origin path choices</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>42</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Alien Physiology: Human medicae tools/tests suffer a -20 penalty when used on an Aeldari.; Waystone (Soul Stone): Protects the character's soul upon death from being consumed by She Who Thirsts.</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans).</t>
+          <t>Alien Physiology: Human medicae tools/tests suffer a -20 penalty when used on an Aeldari.; Waystone (Soul Stone): Protects the character's soul upon death from being consumed by She Who Thirsts.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Pilot (Personal / Jump Pack), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Catfall, Leap Up, Swift Attack, Ambidextrous, Two-Weapon Wielder (Melee/Ballistic), Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
+          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Pilot (Personal / Jump Pack), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shuriken Pistol, Eldar Power Sword, Aeldari Mesh Armour (AP 3), Waystone, Eldar Jump Pack or Cameleoline Cloak. Secret (GM Only): Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
+          <t>Catfall, Leap Up, Swift Attack, Ambidextrous, Two-Weapon Wielder (Melee/Ballistic), Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shuriken Pistol, Eldar Power Sword, Aeldari Mesh Armour (AP 3), Waystone, Eldar Jump Pack or Cameleoline Cloak. Secret (GM Only): Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council. Favour Owed: Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Possesses an illicitly acquired Spirit Stone belonging to an Eldar Craftworld Seer Council.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Swashbuckling Dynasty Heir (Rogue Trader) sanctuary aboard the Apex Predator while fleeing Craftworld trackers.</t>
         </is>
@@ -3544,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3585,401 +3634,408 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rogue Trader</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A charismatic, front-line duelist who leads expeditions from the front rather than from the safety of the flagship bridge.</t>
+          <t>Rogue Trader</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Serves as the tactical linchpin. Uses high Fellowship and Command to manipulate the Space Hulk Alert Level, direct Hostile AI targets, and generate extra Momentum Pool points for the party.</t>
+          <t>A charismatic, front-line duelist who leads expeditions from the front rather than from the safety of the flagship bridge.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7,500 XP (Unique Rogue Trader)</t>
+          <t>Serves as the tactical linchpin. Uses high Fellowship and Command to manipulate the Space Hulk Alert Level, direct Hostile AI targets, and generate extra Momentum Pool points for the party.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,500 XP (Unique Rogue Trader)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Noble Born</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vaunted</t>
+          <t>Noble Born</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duty Bound</t>
+          <t>Vaunted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>High Vendetta</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Renown</t>
+          <t>High Vendetta</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rogue Trader</t>
+          <t>Renown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duty Bound: Duty to Dynasty</t>
+          <t>Rogue Trader</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Duty Bound: Duty to Dynasty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>42</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Exceptional Leader (Free Action once per round: Grant an ally within sight/hearing +10% to any one test).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Exceptional Leader (Free Action once per round: Grant an ally within sight/hearing +10% to any one test).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Command, Commerce, Charm, Evaluate, Literacy, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Inquiry, Dodge.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Air of Authority, Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Renowned Warrant, Peer (Nobility), Decadence.</t>
+          <t>Command, Commerce, Charm, Evaluate, Literacy, Scholastic Lore (Astromancy), Speak Language (High Gothic, Low Gothic), Inquiry, Dodge.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Common-Craftsmanship Plasma Pistol, Best-Craftsmanship Power Sword, Enforcer Light Carapace (AP 5), Xeno-pelt Cloak, Fine Clothing, Micro-bead. Secret (GM Only): The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago. Favour Owed: Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
+          <t>Air of Authority, Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Renowned Warrant, Peer (Nobility), Decadence.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Common-Craftsmanship Plasma Pistol, Best-Craftsmanship Power Sword, Enforcer Light Carapace (AP 5), Xeno-pelt Cloak, Fine Clothing, Micro-bead. Secret (GM Only): The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago. Favour Owed: Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The physical Warrant of Trade held by the Dynasty is a high-grade counterfeit produced two centuries ago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes a debt to a Cold Trade syndicate boss on Footfall who provided emergency financing for the Apex Predator.</t>
         </is>
@@ -3996,7 +4052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4037,401 +4093,408 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Explorator</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>An inquisitive Mechanicus Magos-Explorator who views megastructures as holy cathedrals of the Omnissiah awaiting sanctification.</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Primary utility specialist. Critical for opening locked/sealed bulkheads, disarming plasma/environmental hazard tiles, and converting Archeotech Discovery Cards into permanent Dynasty Profit Factor.</t>
+          <t>An inquisitive Mechanicus Magos-Explorator who views megastructures as holy cathedrals of the Omnissiah awaiting sanctification.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Primary utility specialist. Critical for opening locked/sealed bulkheads, disarming plasma/environmental hazard tiles, and converting Archeotech Discovery Cards into permanent Dynasty Profit Factor.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Forge World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>Forge World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Renegade</t>
+          <t>Savant</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calamity</t>
+          <t>Renegade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Endurance</t>
+          <t>Calamity</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Explorator</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Renegade: Free-Thinker</t>
+          <t>Explorator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Renegade: Free-Thinker</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>30</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Explorator Implants (Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Explorator Implants (Mechanicus Implants Trait + 2 Common-Craftsmanship Bionics).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Tech-Use (+10), Logic, Trade (Technomat), Medicae, Security, Awareness.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Technical Knock, Autosanguine, Nerves of Steel, Light Sleeper.</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Tech-Use (+10), Logic, Trade (Technomat), Medicae, Security, Awareness.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace (AP 5), Servo-Skull Familiar, Combi-tool, Multikey, Sacred Unguents. Secret (GM Only): Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence. Favour Owed: Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Logis Implant, Technical Knock, Autosanguine, Nerves of Steel, Light Sleeper.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Good-Craftsmanship Power Axe, Good-Craftsmanship Hellgun, Enforcer Light Carapace (AP 5), Servo-Skull Familiar, Combi-tool, Multikey, Sacred Unguents. Secret (GM Only): Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence. Favour Owed: Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Scrubbed Mechanicus log entries to cover up the discovery of a semi-functional Abominable Intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Heretek Tech-Acolyte for securing restricted cogitator schematics without notifying Mars.</t>
         </is>
@@ -4448,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4489,401 +4552,408 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Arch-Militant</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A hardened, scarred ex-Naval Armsman specializing in close-quarters boarding actions, hallway breaches, and point-blank crowd control.</t>
+          <t>Arch-Militant</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Front-line tank and hallway anchor. Holds narrow corridors against waves of hostiles.</t>
+          <t>A hardened, scarred ex-Naval Armsman specializing in close-quarters boarding actions, hallway breaches, and point-blank crowd control.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Front-line tank and hallway anchor. Holds narrow corridors against waves of hostiles.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Death World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stubjack</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Criminal</t>
+          <t>Stubjack</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hand of War</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vengeance</t>
+          <t>The Hand of War</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arch-Militant</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Criminal: Wanted Fugitive</t>
+          <t>Arch-Militant</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Criminal: Wanted Fugitive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>40</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Weapon Master (+10% to hit, +2 Damage, and +2 Initiative when using weapons of a chosen class, e.g., Basic/Shotguns or Flamers).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Weapon Master (+10% to hit, +2 Damage, and +2 Initiative when using weapons of a chosen class, e.g., Basic/Shotguns or Flamers).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (War), Dodge, Intimidate (+10), Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Hatred (Pirates/Mutants), Sound Constitution, Bulging Biceps.</t>
+          <t>Common Lore (War), Dodge, Intimidate (+10), Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Naval Shotcannon (or Good-Craftsmanship Hellgun), Mono-edged Boarding Cutlass, Enforcer Light Carapace (AP 5), Micro-bead, Stimm (3 doses), Manacles. Secret (GM Only): Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity. Favour Owed: Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Hatred (Pirates/Mutants), Sound Constitution, Bulging Biceps.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Naval Shotcannon (or Good-Craftsmanship Hellgun), Mono-edged Boarding Cutlass, Enforcer Light Carapace (AP 5), Micro-bead, Stimm (3 doses), Manacles. Secret (GM Only): Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity. Favour Owed: Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Led a brief mutiny aboard an Imperial Navy Cruiser before assuming a dead officer's identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Inquisitorial Agent (Seneschal) for expunging navy desertion records from regional databases.</t>
         </is>
@@ -4900,7 +4970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4941,401 +5011,408 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Navigator</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A noble-born mutant whose Warp Eye sees both the tides of the Immaterium and the latent warp-bleeds of precursor architecture.</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scout and crowd-controller. Uses Psyniscience to scout unopened tiles through bulkheads and fires the Lidless Stare down choke points.</t>
+          <t>A noble-born mutant whose Warp Eye sees both the tides of the Immaterium and the latent warp-bleeds of precursor architecture.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Scout and crowd-controller. Uses Psyniscience to scout unopened tiles through bulkheads and fires the Lidless Stare down choke points.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Void Born</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scapegrace</t>
+          <t>Void Born</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chosen by Destiny</t>
+          <t>Scapegrace</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dark Voyage</t>
+          <t>Chosen by Destiny</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pride</t>
+          <t>Dark Voyage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Pride</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chosen by Destiny: Seeker of Truth</t>
+          <t>Navigator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Chosen by Destiny: Seeker of Truth</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>28</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Warp Eye: Grants access to Navigator Powers (starts with The Lidless Stare).; Shipwise &amp; Void Accustomed: Immune to space travel sickness; zero-G is not treated as difficult terrain.; Grants access to Navigator Powers (starts with The Lidless Stare).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warp Eye: Grants access to Navigator Powers (starts with The Lidless Stare).; Shipwise &amp; Void Accustomed: Immune to space travel sickness; zero-G is not treated as difficult terrain.; Grants access to Navigator Powers (starts with The Lidless Stare).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Psyniscience (+10), Scholastic Lore (Astromancy), Awareness.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Navigator, Pistol Weapon Training (Universal), Foresight, Resistance (Fear), Dark Soul, Warp Sense.</t>
+          <t>Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Psyniscience (+10), Scholastic Lore (Astromancy), Awareness.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour (AP 3), Nobilite Robes, Silk Headscarf/Blindfold, Emperor's Tarot Deck. Secret (GM Only): Navigator mutations are accelerating beyond house-sanctioned parameters. Favour Owed: Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
+          <t>Navigator, Pistol Weapon Training (Universal), Foresight, Resistance (Fear), Dark Soul, Warp Sense.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best-Craftsmanship Hellpistol, Best-Craftsmanship Metal Staff, Best-Craftsmanship Xeno-mesh Armour (AP 3), Nobilite Robes, Silk Headscarf/Blindfold, Emperor's Tarot Deck. Secret (GM Only): Navigator mutations are accelerating beyond house-sanctioned parameters. Favour Owed: Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Navigator mutations are accelerating beyond house-sanctioned parameters.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Navigator mutations are accelerating beyond house-sanctioned parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Beast-Master Privateer (Void-Master) for saving a personal servant during an exotic beast breach.</t>
         </is>
@@ -5352,7 +5429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5393,251 +5470,256 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ork Weirdboy Career Path</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ork Freebooter (Alternate Rank: Weirdboy)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Xenos Battle Psyker and Void Navigator.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Xenos Battle Psyker and Void Navigator.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ork</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ork Freebooter</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Origin path choices</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>36</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5649,115 +5731,127 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Da Power of Waaagh!: Gains Psy Rating bonuses from nearby Orks; rolls on the Weird Fings and 'Eadbang tables instead of standard Psychic Phenomena.; Throo Da Kosmos: Navigates the Warp by instinct using Survival in place of Navigation (Warp).</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Orkoid Physiology (Unnatural Toughness (x2), Sturdy, Iron Jaw, True Grit).</t>
+          <t>Da Power of Waaagh!: Gains Psy Rating bonuses from nearby Orks; rolls on the Weird Fings and 'Eadbang tables instead of standard Psychic Phenomena.; Throo Da Kosmos: Navigates the Warp by instinct using Survival in place of Navigation (Warp).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Orkoid Physiology (Unnatural Toughness (x2), Sturdy, Iron Jaw, True Grit).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Awareness, Common Lore (Orks, War), Psyniscience, Speak Language (Low Gothic, Ork), Survival.</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Psy Rating 2, Da Power of Waaagh!, Throo Da Kosmos, Minderz, Peer (Own Clan), Xenos Weapon Training (Ork).</t>
+          <t>Awareness, Common Lore (Orks, War), Psyniscience, Speak Language (Low Gothic, Ork), Survival.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Copper channelling rod, Squig-hide coat and leggings, Choppa, Slugga, 2 Minderz bodyguards. Secret (GM Only): Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team. Favour Owed: Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
+          <t>Psy Rating 2, Da Power of Waaagh!, Throo Da Kosmos, Minderz, Peer (Own Clan), Xenos Weapon Training (Ork).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Copper channelling rod, Squig-hide coat and leggings, Choppa, Slugga, 2 Minderz bodyguards. Secret (GM Only): Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team. Favour Owed: Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accidentally destroyed his former Freebooter Kaptain’s flagship with uncontrolled psychic discharge and blamed it on a Space Marine strike team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Red Consecrator (Missionary) for refraining from executing his Minderz during their initial encounter.</t>
         </is>
@@ -5774,7 +5868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5815,195 +5909,192 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Career</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Missionary (Alternate Rank: Red Consecrator)</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Career</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Missionary (Alternate Rank: Red Consecrator)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Role in crew</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Martial zealot and front-line shock trooper who treats melee combat as a form of sacred worship.</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XP total</t>
+          <t>Role in crew</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>Martial zealot and front-line shock trooper who treats melee combat as a form of sacred worship.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portrait URL</t>
+          <t>XP total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t># — ORIGIN PATH —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>blank where the character has none (xenos)</t>
+          <t>Portrait URL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Home World</t>
+          <t># — ORIGIN PATH —</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Death World</t>
+          <t>blank where the character has none (xenos)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Birthright</t>
+          <t>Home World</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stubjack</t>
+          <t>Death World</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lure of the Void</t>
+          <t>Birthright</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duty Bound</t>
+          <t>Stubjack</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Lure of the Void</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hand of War</t>
+          <t>Duty Bound</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Trials</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vengeance</t>
+          <t>The Hand of War</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Career (origin step)</t>
+          <t>Motivation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Missionary</t>
+          <t>Vengeance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origin path choices</t>
+          <t>Career (origin step)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duty Bound: Duty to Humanity; Missionary: Red Consecrator Alt Rank</t>
+          <t>Missionary</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t># — FINAL CHARACTERISTICS —</t>
+          <t>Origin path choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>already include origin modifiers and advances — do NOT reapply</t>
+          <t>Duty Bound: Duty to Humanity; Missionary: Red Consecrator Alt Rank</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weapon Skill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>44</v>
+          <t># — FINAL CHARACTERISTICS —</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>already include origin modifiers and advances — do NOT reapply</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ballistic Skill</t>
+          <t>Weapon Skill</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Ballistic Skill</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6013,198 +6104,208 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Willpower</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t># — DERIVED —</t>
-        </is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Final wounds</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t># — DERIVED —</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Final fate points</t>
+          <t>Final wounds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Psy rating</t>
+          <t>Final fate points</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t># — ABILITIES —</t>
+          <t>Psy rating</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Special ability</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Pure Faith: Immune to Daemonic Presence; can spend or burn Fate Points to resist Warp corruption and inspire allies.; Rage of the Zealot: Inflicts Righteous Fury on a result of 9 or 10 when attacking hated foes with melee weapons.</t>
+          <t># — ABILITIES —</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Origin / trait modifiers</t>
+          <t>Special ability</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pure Faith: Immune to Daemonic Presence; can spend or burn Fate Points to resist Warp corruption and inspire allies.; Rage of the Zealot: Inflicts Righteous Fury on a result of 9 or 10 when attacking hated foes with melee weapons.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Psychic powers</t>
+          <t>Origin / trait modifiers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t># — SKILLS, TALENTS, WARGEAR —</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semicolon separated</t>
+          <t>Psychic powers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t># — SKILLS, TALENTS, WARGEAR —</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Common Lore (Imperial Creed, Imperium, War), Command, Dodge, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
+          <t>semicolon separated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Talents</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Hatred (Psykers), Hatred (Mutants), Litany of Hate, Rage of the Zealot.</t>
+          <t>Common Lore (Imperial Creed, Imperium, War), Command, Dodge, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Talents</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eviscerator two-handed chainsword, Flamer, Guard Flak Armour, Ecclesiarchal Robes, Aquila Pendant, Micro-bead. Secret (GM Only): Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities. Favour Owed: Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Hatred (Psykers), Hatred (Mutants), Litany of Hate, Rage of the Zealot.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Eviscerator two-handed chainsword, Flamer, Guard Flak Armour, Ecclesiarchal Robes, Aquila Pendant, Micro-bead. Secret (GM Only): Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities. Favour Owed: Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Collects and maintains unholy relics under the rationale of using them to provoke and destroy warp entities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Owes the Untouchable Witch Finder for breaking a witch's dominate mental hold during a purging raid.</t>
         </is>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>10,000 XP</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>6,500 XP</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>7,500 XP</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000 XP</t>
+          <t>10,000 XP</t>
         </is>
       </c>
     </row>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable, Infused Knowledge.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Armour of Contempt, Peer (Inquisition), Peer (Academic), Rival (Rival Inquisitorial Faction), Unremarkable.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Medicae, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Tech-Use (+10), Trade (Archaeologist, Technomat).</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Adeptus Mechanicus, Archeotech, Xenos), Literacy, Logic, Speak Language (Explorator Binary, Low Gothic, Techna-Lingua), Trade (Archaeologist, Technomat).</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Awareness, Common Lore (Imperial Navy, War), Dodge, Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
+          <t>Awareness, Common Lore (Imperial Navy, War), Drive (Ground Vehicle), Forbidden Lore (Xenos), Navigation (Stellar), Pilot (Flyers, Space Craft), Scholastic Lore (Astromancy, Beasts), Speak Language (Low Gothic), Survival, Wrangling.</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Psy Rating 3, Resistance (Psychic Powers), Strong Minded, Unshakeable Faith, Warp Sense.</t>
+          <t>Pistol Weapon Training (Universal), Melee Weapon Training (Primitive), Resistance (Psychic Powers), Unshakeable Faith.</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Pilot (Personal / Jump Pack), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
+          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Catfall, Leap Up, Swift Attack, Ambidextrous, Two-Weapon Wielder (Melee/Ballistic), Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
+          <t>Catfall, Leap Up, Ambidextrous, Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP (Unique Rogue Trader)</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Tech-Use (+10), Logic, Trade (Technomat), Medicae, Security, Awareness.</t>
+          <t>Common Lore (Machine Cult, Tech), Forbidden Lore (Archeotech, Adeptus Mechanicus), Logic, Trade (Technomat), Security, Awareness.</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Common Lore (War), Dodge, Intimidate (+10), Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
+          <t>Common Lore (War), Dodge, Scholastic Lore (Tactica Imperialis), Secret Tongue (Military), Survival, Awareness.</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Hatred (Pirates/Mutants), Sound Constitution, Bulging Biceps.</t>
+          <t>Basic Weapon Training (Universal), Pistol Weapon Training (Universal), Melee Weapon Training (Universal), Thrown Weapon Training (Universal), Quick Draw, Sound Constitution.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,500 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Psyniscience (+10), Scholastic Lore (Astromancy), Awareness.</t>
+          <t>Common Lore (Navis Nobilite), Forbidden Lore (Navigators, Warp), Navigation (Stellar, Warp), Scholastic Lore (Astromancy), Awareness.</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10,000 XP</t>
+          <t>5,000 XP</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Common Lore (Imperial Creed, Imperium, War), Command, Dodge, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
+          <t>Common Lore (Imperial Creed, Imperium, War), Command, Forbidden Lore (Heresy), Intimidate, Medicae, Scholastic Lore (Imperial Creed), Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Hatred (Psykers), Hatred (Mutants), Litany of Hate, Rage of the Zealot.</t>
+          <t>Basic Weapon Training (Universal), Melee Weapon Training (Universal), Flame Weapon Training (Universal), Pure Faith, Unshakeable Faith, Rage of the Zealot.</t>
         </is>
       </c>
     </row>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Forbidden Lore (Archeotech, The Inquisition), Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
+          <t>Barter, Commerce, Common Lore (Imperium, Underworld), Deceive, Evaluate, Inquiry, Interrogation, Literacy, Logic, Scrutiny, Secret Tongue (Administratum, Rogue Trader), Speak Language (High Gothic, Low Gothic, Trader’s Cant).</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Awareness, Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Speak Language (High Gothic, Low Gothic).</t>
+          <t>Awareness, Ciphers (Astropath Code), Common Lore (Adeptus Astra Telepathica), Forbidden Lore (Psykers, Warp), Invocation, Literacy, Medicae, Psyniscience, Scholastic Lore (Cryptology), Speak Language (High Gothic, Low Gothic).</t>
         </is>
       </c>
     </row>
@@ -3383,8 +3383,10 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>48</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -3492,7 +3494,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans).</t>
+          <t>Aeldari Physiology (+10 Agility, +5 Perception, -5 Toughness, -5 Strength compared to base humans). Species Traits: Unnatural Agility (×2), Matchless Grace, Waystone, Non-Imperial, Speak Not Unto the Alien, Cybernetic Rejection.</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3525,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acrobatics, Awareness, Dodge (+10), Navigation (Stellar), Secret Tongue (Eldar), Speak Language (Eldar, Low Gothic).</t>
+          <t>Acrobatics, Awareness, Common Lore (Eldar), Dodge (+10), Forbidden Lore (Xenos), Navigation (Stellar), Secret Tongue (Eldar), Silent Move, Speak Language (Eldar, Low Gothic).</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3537,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Catfall, Leap Up, Ambidextrous, Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
+          <t>Catfall, Leap Up, Ambidextrous, Heightened Senses (Sight, Hearing), Sprint, Exotic Weapon Training (Shuriken Pistol, Shuriken Catapult), Eldar Weapon Training.</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5769,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Orkoid Physiology (Unnatural Toughness (x2), Sturdy, Iron Jaw, True Grit).</t>
+          <t>Orkoid Physiology (Unnatural Toughness (×2), Size (Hulking), Iron Jaw, True Grit, Make Do).</t>
         </is>
       </c>
     </row>

--- a/characters.xlsx
+++ b/characters.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1277,41 +1277,53 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wargear</t>
+          <t>Elite Advances</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
+          <t>Untouchable (1) (Trait, 500 XP)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t># — GM —</t>
+          <t>Wargear</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Condemnor Boltgun with Purgatus Stake-Bolts, Web Pistol, Xeno-mesh Armour, Autoquill, Dataslate, Multikey, Manacles. Secret (GM Only): Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships. Favour Owed: Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Secret</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
+          <t># — GM —</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Running private evaluations on the party's psykers for markings that warrant immediate transfer to Black Ships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Favour owed</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Owes the Exiled House Visscher Navigator for steering through a dead-space anomaly during an escape attempt.</t>
         </is>
